--- a/all_output.xlsx
+++ b/all_output.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\graph_to_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E241777B-2962-4F20-9071-8D1600256CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC6202B-4836-47A2-98D6-A7B0D4B37354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{70A44F9F-0021-4FBD-8DCA-C0237865C5CF}"/>
   </bookViews>
@@ -1219,6 +1219,1282 @@
         <a:xfrm>
           <a:off x="0" y="147117218"/>
           <a:ext cx="9465361" cy="5176090"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>889</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>926</xdr:row>
+      <xdr:rowOff>63128</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Picture 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8229548-9DF3-4798-A83C-9FA9F75B0141}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="150909950"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>927</xdr:row>
+      <xdr:rowOff>61188</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>964</xdr:row>
+      <xdr:rowOff>124318</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Picture 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6206B53-D098-44AB-BBCC-E72EA0F7E8A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="157421733"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>966</xdr:row>
+      <xdr:rowOff>138677</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1004</xdr:row>
+      <xdr:rowOff>32053</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Picture 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B314910A-C6D3-4D2E-A03E-6EE0C8E66FE7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="164119568"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1006</xdr:row>
+      <xdr:rowOff>46412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1043</xdr:row>
+      <xdr:rowOff>109541</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Picture 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48514E8A-C9D8-40C1-B145-F5F68A085CA7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="170817402"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1045</xdr:row>
+      <xdr:rowOff>123900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1083</xdr:row>
+      <xdr:rowOff>17276</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Picture 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDC74B5B-14F2-4B87-A588-31473A53B8EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="177515237"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1085</xdr:row>
+      <xdr:rowOff>31635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1122</xdr:row>
+      <xdr:rowOff>94765</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Picture 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC2A27D4-F927-4C5A-9419-73BC972B59E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="184213071"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1124</xdr:row>
+      <xdr:rowOff>109123</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1162</xdr:row>
+      <xdr:rowOff>2500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Picture 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D02B884-A472-4B01-AF17-69FAEC1A2682}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="190910905"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1164</xdr:row>
+      <xdr:rowOff>16859</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1201</xdr:row>
+      <xdr:rowOff>79987</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="Picture 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6426540E-AB90-44D1-9E85-B76920C39F72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="197608740"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1203</xdr:row>
+      <xdr:rowOff>94346</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1240</xdr:row>
+      <xdr:rowOff>157476</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="Picture 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4B07310-D57C-4080-BD80-D0A47636F574}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="204306574"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1244</xdr:row>
+      <xdr:rowOff>18381</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1281</xdr:row>
+      <xdr:rowOff>81509</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="Picture 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15CF086F-2160-416E-97AC-EE95AACB6CEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="211190460"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1283</xdr:row>
+      <xdr:rowOff>95868</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1320</xdr:row>
+      <xdr:rowOff>158997</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Picture 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB0D45CC-0D56-463A-A3FA-389B5830E31B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="217888294"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1324</xdr:row>
+      <xdr:rowOff>19902</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1361</xdr:row>
+      <xdr:rowOff>83031</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="Picture 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E991EA21-9340-4810-B407-4E3352EF1F45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="224772179"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1363</xdr:row>
+      <xdr:rowOff>97390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1400</xdr:row>
+      <xdr:rowOff>160519</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Picture 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC02954D-3245-4EB2-A69B-92B56A18CC9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="231470014"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1403</xdr:row>
+      <xdr:rowOff>5125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1440</xdr:row>
+      <xdr:rowOff>68255</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Picture 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE77D369-77C7-4375-97DD-F8AE2E39232C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="238167848"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1442</xdr:row>
+      <xdr:rowOff>82613</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1479</xdr:row>
+      <xdr:rowOff>145742</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Picture 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91A37B0B-9D21-4EED-9DB5-BA351916BFAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="244865682"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1481</xdr:row>
+      <xdr:rowOff>160101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1519</xdr:row>
+      <xdr:rowOff>53477</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D982218D-CD61-4E20-BEB2-FB1CA5FFECCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="251563517"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1521</xdr:row>
+      <xdr:rowOff>67836</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1558</xdr:row>
+      <xdr:rowOff>130966</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Picture 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2606121B-011C-4683-9598-D665F48FDCF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="258261351"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1560</xdr:row>
+      <xdr:rowOff>145325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1598</xdr:row>
+      <xdr:rowOff>38701</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Picture 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{956F084B-4299-4413-89D8-14F170AC63C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="264959186"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1601</xdr:row>
+      <xdr:rowOff>69358</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1638</xdr:row>
+      <xdr:rowOff>132488</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="Picture 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A971D71-B02F-4721-B691-506C6DC55489}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="271843071"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1640</xdr:row>
+      <xdr:rowOff>146846</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1678</xdr:row>
+      <xdr:rowOff>40223</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="Picture 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD1F45F4-4180-4007-8666-FAAF67515CB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="278540905"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1681</xdr:row>
+      <xdr:rowOff>70880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1718</xdr:row>
+      <xdr:rowOff>134009</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Picture 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1887BB9-92B2-4DD7-8844-A05F5594356C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="285424791"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1720</xdr:row>
+      <xdr:rowOff>148368</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1758</xdr:row>
+      <xdr:rowOff>41745</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Picture 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F332CA17-0C18-466A-AFB8-ECFAA5F71E41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="292122625"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1760</xdr:row>
+      <xdr:rowOff>56104</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1797</xdr:row>
+      <xdr:rowOff>119232</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Picture 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92F222E8-56CC-45A9-A2AC-C362F062628B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="298820460"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1799</xdr:row>
+      <xdr:rowOff>133591</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1837</xdr:row>
+      <xdr:rowOff>26967</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Picture 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C35679D6-5241-4A41-B132-5A6AB27532A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="305518294"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1839</xdr:row>
+      <xdr:rowOff>41326</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1876</xdr:row>
+      <xdr:rowOff>104455</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C72DD73E-E4C4-41A1-8C4B-62776C2EDF80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="312216128"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1878</xdr:row>
+      <xdr:rowOff>118814</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1916</xdr:row>
+      <xdr:rowOff>12190</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6E93374-7E51-4686-8F3C-A9799912EF87}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="318913963"/>
+          <a:ext cx="11191813" cy="6343970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1919</xdr:row>
+      <xdr:rowOff>42848</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1956</xdr:row>
+      <xdr:rowOff>105977</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9116A207-32B8-42BF-AECB-6B4EF1422428}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="325797848"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1958</xdr:row>
+      <xdr:rowOff>120335</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>1996</xdr:row>
+      <xdr:rowOff>13712</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{865C04FF-758E-47C7-90F2-A91D40BF88D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="332495682"/>
+          <a:ext cx="11191813" cy="6343971"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1998</xdr:row>
+      <xdr:rowOff>28071</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>648298</xdr:colOff>
+      <xdr:row>2035</xdr:row>
+      <xdr:rowOff>91200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C62EF0BE-21BC-48C0-9568-EB0D0FF37C60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="339193517"/>
+          <a:ext cx="11191813" cy="6343970"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
